--- a/src/test/resources/RecruiterDetails.xlsx
+++ b/src/test/resources/RecruiterDetails.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="41">
   <si>
     <t>name</t>
   </si>
@@ -137,6 +137,18 @@
   </si>
   <si>
     <t>Marley David (marley)</t>
+  </si>
+  <si>
+    <t>Dec 30, 2025</t>
+  </si>
+  <si>
+    <t>Jan 23, 2026</t>
+  </si>
+  <si>
+    <t>Jan 29, 2026</t>
+  </si>
+  <si>
+    <t>Jan 10, 2026</t>
   </si>
 </sst>
 </file>
@@ -492,7 +504,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>11</v>
@@ -515,10 +527,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>12</v>
@@ -558,7 +570,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>

--- a/src/test/resources/RecruiterDetails.xlsx
+++ b/src/test/resources/RecruiterDetails.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="43">
   <si>
     <t>name</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t>Jan 10, 2026</t>
+  </si>
+  <si>
+    <t>Feb 10, 2026</t>
+  </si>
+  <si>
+    <t>Feb 15, 2026</t>
   </si>
 </sst>
 </file>
@@ -504,10 +510,10 @@
         <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>12</v>
@@ -570,7 +576,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>27</v>
@@ -616,7 +622,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>35</v>
